--- a/data/trans_orig/P42C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P42C-Clase-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2012 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121809</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105195</t>
+          <t>105390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140632</t>
+          <t>140233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>121809</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>105195</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>140632</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>42,97%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>37,11%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>49,61%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>161687</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142864</t>
+          <t>143263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178301</t>
+          <t>178106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>161687</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>142864</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>178301</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>57,03%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>50,39%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>62,89%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283496</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283496</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>283496</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>283496</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>283496</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116567</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134602</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99621</t>
+          <t>97679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>116567</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>99621</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>135820</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>41,29%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>35,28%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>48,1%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165777</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146524</t>
+          <t>147742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182723</t>
+          <t>184665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>165777</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>146524</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>182723</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>58,71%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>51,9%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>64,72%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>251</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>282344</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>282344</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>282344</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>282344</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>282344</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>282344</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56867</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>43975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70680</t>
+          <t>71308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>56867</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>44252</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>70680</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>32,83%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158416</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144603</t>
+          <t>143975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171031</t>
+          <t>171308</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>158416</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>144603</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>171031</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>73,58%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>67,17%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>79,44%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>203</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215283</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215283</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>215283</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>215283</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>215283</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135138</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158983</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115153</t>
+          <t>114414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158500</t>
+          <t>158983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>135138</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>115153</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>158500</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>21,91%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481528</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>457683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>502252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458166</t>
+          <t>457683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501513</t>
+          <t>502252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>481528</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>458166</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>501513</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>78,09%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>74,3%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>81,33%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>569</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>616666</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>616666</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>616666</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>616666</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>616666</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>616666</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2094,37 +1614,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93327</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112071</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76206</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114251</t>
+          <t>112071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,47 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>93327</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>76206</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -2207,37 +1692,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>504603</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>485859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>523018</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>483679</t>
+          <t>485859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>521724</t>
+          <t>523018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,47 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>504603</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>483679</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>521724</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>80,89%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>87,26%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -2320,37 +1770,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>550</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>597930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>597930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>597930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2384,41 +1834,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>597930</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>597930</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>597930</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2437,37 +1852,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130975</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152074</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +1897,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110618</t>
+          <t>110579</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153090</t>
+          <t>152074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,47 +1912,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>130975</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>110618</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>153090</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -2550,37 +1930,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>570</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>609145</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>588046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>629541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +1975,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>587030</t>
+          <t>588046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>629502</t>
+          <t>629541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,47 +1990,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>609145</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>587030</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>629502</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>82,3%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>79,32%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>85,05%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2008,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>692</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>740120</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>740120</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>740120</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2727,41 +2072,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>740120</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>740120</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>740120</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2780,37 +2090,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>654683</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>607037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>703914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2135,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>607333</t>
+          <t>607037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>699439</t>
+          <t>703914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,47 +2150,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>654683</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>607333</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>699439</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -2893,37 +2168,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2081156</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2031925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2128802</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2213,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2036400</t>
+          <t>2031925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2128506</t>
+          <t>2128802</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,47 +2228,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2081156</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2036400</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2128506</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>74,43%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -3006,37 +2246,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2735839</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2735839</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2735839</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3070,41 +2310,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2520</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2735839</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2735839</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2735839</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3118,7 +2323,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3126,7 +2331,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3141,7 +2345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3160,25 +2364,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2016 (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +2386,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3198,17 +2395,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3279,41 +2465,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3336,13 +2487,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3357,37 +2501,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103761</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +2546,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88909</t>
+          <t>88529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122970</t>
+          <t>122197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,47 +2561,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>103761</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>88909</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>122970</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -3470,37 +2579,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>197</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204685</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>219917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +2624,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185476</t>
+          <t>186249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>219917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,47 +2639,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>204685</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>185476</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>219537</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>66,36%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>60,13%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>71,18%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
@@ -3583,37 +2657,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308446</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3647,41 +2721,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>308446</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>308446</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>308446</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3700,37 +2739,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92676</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +2784,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>76550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111915</t>
+          <t>111193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,47 +2799,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>92676</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>77755</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>111915</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>33,49%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -3813,37 +2817,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241469</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +2862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222230</t>
+          <t>222952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256390</t>
+          <t>257595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,47 +2877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>241469</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>222230</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>256390</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>66,51%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>76,73%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -3926,37 +2895,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>316</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334145</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334145</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334145</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3990,41 +2959,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>334145</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>334145</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>334145</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4043,37 +2977,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +3022,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,47 +3037,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>15864</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>9771</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>24690</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -4156,37 +3055,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125947</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132283</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +3100,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117121</t>
+          <t>116780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132040</t>
+          <t>132283</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,47 +3115,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>125947</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>117121</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>132040</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>82,59%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -4269,37 +3133,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141811</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141811</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4333,41 +3197,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>141811</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>141811</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>141811</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4386,37 +3215,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98542</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +3260,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79334</t>
+          <t>80406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117911</t>
+          <t>118904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,47 +3275,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>98542</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>79334</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>117911</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -4499,37 +3293,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>573</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>590480</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>570118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>608616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +3338,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571111</t>
+          <t>570118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609688</t>
+          <t>608616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,47 +3353,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>590480</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>571111</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>609688</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>85,7%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>82,89%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -4612,37 +3371,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689022</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689022</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4676,41 +3435,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>689022</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>689022</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>689022</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4729,37 +3453,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +3498,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51857</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,47 +3513,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>36950</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>26348</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>51857</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4842,37 +3531,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>530761</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>516282</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +3576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>515854</t>
+          <t>516282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>541363</t>
+          <t>541800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,47 +3591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>530761</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>515854</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>541363</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>90,87%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -4955,37 +3609,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>538</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>567711</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>567711</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>567711</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5019,41 +3673,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>567711</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>567711</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>567711</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5072,37 +3691,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79415</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +3736,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64331</t>
+          <t>64656</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99216</t>
+          <t>98221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,47 +3751,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>79415</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>64331</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>99216</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -5185,37 +3769,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>645243</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>626437</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>660002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +3814,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>625442</t>
+          <t>626437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>660327</t>
+          <t>660002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,47 +3829,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>645243</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>625442</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>660327</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>89,04%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -5298,37 +3847,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>666</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724658</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724658</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724658</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5362,41 +3911,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>724658</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>724658</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>724658</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5415,37 +3929,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>402</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427208</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388046</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>464711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +3974,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>389544</t>
+          <t>388046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>468838</t>
+          <t>464711</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,47 +3989,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>427208</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>389544</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>468838</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -5528,37 +4007,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2338585</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2301082</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2377747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +4052,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2296955</t>
+          <t>2301082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2376249</t>
+          <t>2377747</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,47 +4067,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2210</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2338585</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2296955</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2376249</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>84,55%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>83,05%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -5641,37 +4085,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2765793</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2765793</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2765793</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5705,41 +4149,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2765793</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2765793</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2765793</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5753,7 +4162,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5761,7 +4170,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -5776,7 +4184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5795,25 +4203,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +4225,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5833,17 +4234,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5914,41 +4304,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5971,13 +4326,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5992,37 +4340,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124871</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111561</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +4385,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111512</t>
+          <t>111561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139291</t>
+          <t>140322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,47 +4400,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>124871</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>111512</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>139291</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>40,82%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>50,99%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -6105,37 +4418,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148279</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>161589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +4463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133859</t>
+          <t>132828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161638</t>
+          <t>161589</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,47 +4478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>148279</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>133859</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>161638</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>54,28%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>49,01%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>59,18%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -6218,37 +4496,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273150</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6282,41 +4560,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>273150</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>273150</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>273150</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6335,37 +4578,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102447</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +4623,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89703</t>
+          <t>89357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116126</t>
+          <t>115003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,47 +4638,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>102447</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>89703</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>116126</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>43,18%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>37,81%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -6448,37 +4656,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +4701,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121114</t>
+          <t>122237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147537</t>
+          <t>147883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,47 +4716,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>134793</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>121114</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>147537</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>56,82%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>51,05%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>62,19%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -6561,37 +4734,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237240</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237240</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237240</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6625,41 +4798,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>237240</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>237240</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>237240</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6678,37 +4816,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15175</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +4861,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>15175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,47 +4876,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>21561</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>15388</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>28419</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>22,62%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>29,82%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -6791,37 +4894,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73745</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +4939,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66887</t>
+          <t>66269</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79918</t>
+          <t>80131</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,47 +4954,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>73745</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>66887</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>79918</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>77,38%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>70,18%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>83,85%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -6904,37 +4972,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95306</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95306</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6968,41 +5036,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>95306</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>95306</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>95306</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7021,37 +5054,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94031</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79189</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +5099,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79153</t>
+          <t>79189</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109344</t>
+          <t>112135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,47 +5114,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>94031</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>79153</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>109344</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>24,46%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -7134,37 +5132,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353086</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +5177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337773</t>
+          <t>334982</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367964</t>
+          <t>367928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,47 +5192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>353086</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>337773</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>367964</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>78,97%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>75,54%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>82,3%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -7247,37 +5210,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>447117</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>447117</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>447117</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7311,41 +5274,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>447117</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>447117</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>447117</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7364,37 +5292,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +5337,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>33710</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66779</t>
+          <t>68247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,47 +5352,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>31866</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>66779</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -7477,37 +5370,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>684</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>484924</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>502451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +5415,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469382</t>
+          <t>467914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>504295</t>
+          <t>502451</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,47 +5430,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>484924</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>469382</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>504295</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -7590,37 +5448,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536161</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536161</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536161</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7654,41 +5512,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>536161</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>536161</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>536161</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7707,37 +5530,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70111</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +5575,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42412</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67048</t>
+          <t>70111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,47 +5590,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>53966</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>42412</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>67048</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -7820,37 +5608,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>583</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>329387</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>341004</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +5653,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316305</t>
+          <t>313242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340941</t>
+          <t>341004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,47 +5668,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>329387</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>316305</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>340941</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>82,51%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
+          <t>88,95%</t>
         </is>
       </c>
     </row>
@@ -7933,37 +5686,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>658</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>383353</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>383353</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>383353</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7997,41 +5750,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>383353</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>383353</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>383353</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8050,37 +5768,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>684</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>448113</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>395698</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>490137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +5813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>386847</t>
+          <t>395698</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>486282</t>
+          <t>490137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,47 +5828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>448113</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>386847</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>486282</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -8163,37 +5846,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1524214</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1482190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1576629</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +5891,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1486045</t>
+          <t>1482190</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1585480</t>
+          <t>1576629</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,47 +5906,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2431</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1524214</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1486045</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1585480</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>75,34%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>80,39%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -8276,37 +5924,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1972327</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1972327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1972327</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8340,41 +5988,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1972327</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1972327</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1972327</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8388,7 +6001,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8396,7 +6009,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P42C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P42C-Clase-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105390</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140233</t>
+          <t>139880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105390</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140233</t>
+          <t>139880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143263</t>
+          <t>143616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178106</t>
+          <t>179223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143263</t>
+          <t>143616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178106</t>
+          <t>179223</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97679</t>
+          <t>99210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134602</t>
+          <t>135405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97679</t>
+          <t>99210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134602</t>
+          <t>135405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147742</t>
+          <t>146939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184665</t>
+          <t>183134</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147742</t>
+          <t>146939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184665</t>
+          <t>183134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,86%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>42865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71308</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>42865</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71308</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143975</t>
+          <t>145879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171308</t>
+          <t>172418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143975</t>
+          <t>145879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171308</t>
+          <t>172418</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114414</t>
+          <t>115864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158983</t>
+          <t>157825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114414</t>
+          <t>115864</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158983</t>
+          <t>157825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>457683</t>
+          <t>458841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>502252</t>
+          <t>500802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>457683</t>
+          <t>458841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502252</t>
+          <t>500802</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74912</t>
+          <t>75544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112071</t>
+          <t>113088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74912</t>
+          <t>75544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112071</t>
+          <t>113088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>485859</t>
+          <t>484842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>523018</t>
+          <t>522386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485859</t>
+          <t>484842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>523018</t>
+          <t>522386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110579</t>
+          <t>110457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152074</t>
+          <t>153346</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110579</t>
+          <t>110457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152074</t>
+          <t>153346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>588046</t>
+          <t>586774</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>629541</t>
+          <t>629663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>588046</t>
+          <t>586774</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>629541</t>
+          <t>629663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>607037</t>
+          <t>609765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>703914</t>
+          <t>701918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>607037</t>
+          <t>609765</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>703914</t>
+          <t>701918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2031925</t>
+          <t>2033921</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2128802</t>
+          <t>2126074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2031925</t>
+          <t>2033921</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2128802</t>
+          <t>2126074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -2511,12 +2511,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88529</t>
+          <t>87370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122197</t>
+          <t>121199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88529</t>
+          <t>87370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122197</t>
+          <t>121199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -2589,12 +2589,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186249</t>
+          <t>187247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>219917</t>
+          <t>221076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186249</t>
+          <t>187247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219917</t>
+          <t>221076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -2749,12 +2749,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76550</t>
+          <t>75810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111193</t>
+          <t>111302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76550</t>
+          <t>75810</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111193</t>
+          <t>111302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>222952</t>
+          <t>222843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257595</t>
+          <t>258335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222952</t>
+          <t>222843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257595</t>
+          <t>258335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,31%</t>
         </is>
       </c>
     </row>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116780</t>
+          <t>117600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132283</t>
+          <t>132688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116780</t>
+          <t>117600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132283</t>
+          <t>132688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80406</t>
+          <t>80362</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>118834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80406</t>
+          <t>80362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>118834</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -3303,12 +3303,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>570118</t>
+          <t>570188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608616</t>
+          <t>608660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>570118</t>
+          <t>570188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608616</t>
+          <t>608660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>51689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>51689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -3541,12 +3541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>516282</t>
+          <t>516022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>541800</t>
+          <t>541982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>516282</t>
+          <t>516022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>541800</t>
+          <t>541982</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>64621</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98221</t>
+          <t>98644</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>64621</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98221</t>
+          <t>98644</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>626437</t>
+          <t>626014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>660002</t>
+          <t>660037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>626437</t>
+          <t>626014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>660002</t>
+          <t>660037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>388046</t>
+          <t>389853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>464711</t>
+          <t>467916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>388046</t>
+          <t>389853</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>464711</t>
+          <t>467916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2301082</t>
+          <t>2297877</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2377747</t>
+          <t>2375940</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2301082</t>
+          <t>2297877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2377747</t>
+          <t>2375940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>124871</t>
+          <t>136515</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>121531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140322</t>
+          <t>151175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4380,32 +4380,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>124871</t>
+          <t>136515</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>121531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140322</t>
+          <t>151175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -4423,32 +4423,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>148279</t>
+          <t>160956</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132828</t>
+          <t>146296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161589</t>
+          <t>175940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4458,32 +4458,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>148279</t>
+          <t>160956</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132828</t>
+          <t>146296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161589</t>
+          <t>175940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,15%</t>
         </is>
       </c>
     </row>
@@ -4501,17 +4501,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>273150</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273150</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>273150</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>273150</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>273150</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>273150</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>102447</t>
+          <t>114253</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89357</t>
+          <t>101059</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115003</t>
+          <t>128708</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>102447</t>
+          <t>114253</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89357</t>
+          <t>101059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115003</t>
+          <t>128708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -4661,32 +4661,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>134793</t>
+          <t>151517</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122237</t>
+          <t>137062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147883</t>
+          <t>164711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>134793</t>
+          <t>151517</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122237</t>
+          <t>137062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147883</t>
+          <t>164711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -4739,17 +4739,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>237240</t>
+          <t>265770</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>237240</t>
+          <t>265770</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>237240</t>
+          <t>265770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>237240</t>
+          <t>265770</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>237240</t>
+          <t>265770</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>237240</t>
+          <t>265770</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>23678</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>31700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>23678</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>31700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -4899,32 +4899,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73745</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66269</t>
+          <t>73340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80131</t>
+          <t>88091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4934,32 +4934,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73745</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66269</t>
+          <t>73340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80131</t>
+          <t>88091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -4977,17 +4977,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>105040</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>105040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>105040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5012,17 +5012,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>105040</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>105040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>105040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5059,32 +5059,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94031</t>
+          <t>103191</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79189</t>
+          <t>87560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112135</t>
+          <t>118854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5094,32 +5094,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94031</t>
+          <t>103191</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79189</t>
+          <t>87560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112135</t>
+          <t>118854</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -5137,32 +5137,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>353086</t>
+          <t>395182</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334982</t>
+          <t>379519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367928</t>
+          <t>410813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5172,32 +5172,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>353086</t>
+          <t>395182</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>334982</t>
+          <t>379519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367928</t>
+          <t>410813</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -5215,17 +5215,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>447117</t>
+          <t>498373</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>447117</t>
+          <t>498373</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>447117</t>
+          <t>498373</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5250,17 +5250,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>447117</t>
+          <t>498373</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>447117</t>
+          <t>498373</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>447117</t>
+          <t>498373</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5297,32 +5297,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>55292</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33710</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68247</t>
+          <t>67620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5332,32 +5332,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>55292</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33710</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68247</t>
+          <t>67620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -5375,32 +5375,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>484924</t>
+          <t>420925</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467914</t>
+          <t>408597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502451</t>
+          <t>432658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5410,32 +5410,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>484924</t>
+          <t>420925</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>467914</t>
+          <t>408597</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>502451</t>
+          <t>432658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -5453,17 +5453,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536161</t>
+          <t>476217</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536161</t>
+          <t>476217</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536161</t>
+          <t>476217</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>536161</t>
+          <t>476217</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>536161</t>
+          <t>476217</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>536161</t>
+          <t>476217</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5535,32 +5535,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>57291</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>44869</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70111</t>
+          <t>73528</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5570,32 +5570,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>57291</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>44869</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70111</t>
+          <t>73528</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5613,32 +5613,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>329387</t>
+          <t>360764</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>313242</t>
+          <t>344527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>341004</t>
+          <t>373186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5648,32 +5648,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>329387</t>
+          <t>360764</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313242</t>
+          <t>344527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341004</t>
+          <t>373186</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -5691,17 +5691,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>383353</t>
+          <t>418055</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>383353</t>
+          <t>418055</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>383353</t>
+          <t>418055</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5726,17 +5726,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>383353</t>
+          <t>418055</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>383353</t>
+          <t>418055</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>383353</t>
+          <t>418055</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5773,32 +5773,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>448113</t>
+          <t>490220</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>395698</t>
+          <t>458600</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>490137</t>
+          <t>524542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5808,32 +5808,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>448113</t>
+          <t>490220</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>395698</t>
+          <t>458600</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>490137</t>
+          <t>524542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -5851,32 +5851,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1524214</t>
+          <t>1570707</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1482190</t>
+          <t>1536385</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1576629</t>
+          <t>1602327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1524214</t>
+          <t>1570707</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1482190</t>
+          <t>1536385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1576629</t>
+          <t>1602327</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -5929,17 +5929,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1972327</t>
+          <t>2060927</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1972327</t>
+          <t>2060927</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1972327</t>
+          <t>2060927</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5964,17 +5964,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1972327</t>
+          <t>2060927</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1972327</t>
+          <t>2060927</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1972327</t>
+          <t>2060927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
